--- a/outputs/2026-01-30/placeholder_by_entity.xlsx
+++ b/outputs/2026-01-30/placeholder_by_entity.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1720</v>
+        <v>1725</v>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1460</v>
+        <v>1487</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
